--- a/data/upcoming_fights.xlsx
+++ b/data/upcoming_fights.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,6 +438,270 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Justin Gaethje</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Paddy Pimblett</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>January 24, 2026</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Las Vegas, Nevada, USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Sean O'Malley</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Song Yadong</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>January 24, 2026</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Las Vegas, Nevada, USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Waldo Cortes Acosta</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Derrick Lewis</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>January 24, 2026</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Las Vegas, Nevada, USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Natalia Silva</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Rose Namajunas</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>January 24, 2026</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Las Vegas, Nevada, USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Arnold Allen</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Jean Silva</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>January 24, 2026</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Las Vegas, Nevada, USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Umar Nurmagomedov</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Deiveson Figueiredo</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>January 24, 2026</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Las Vegas, Nevada, USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ateba Gautier</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Andrey Pulyaev</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>January 24, 2026</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Las Vegas, Nevada, USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Nikita Krylov</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Modestas Bukauskas</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>January 24, 2026</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Las Vegas, Nevada, USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Alex Perez</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Charles Johnson</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>January 24, 2026</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Las Vegas, Nevada, USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Michael Johnson</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Alexander Hernandez</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>January 24, 2026</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Las Vegas, Nevada, USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Josh Hokit</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Denzel Freeman</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>January 24, 2026</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Las Vegas, Nevada, USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Adam Fugitt</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ty Miller</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>January 24, 2026</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Las Vegas, Nevada, USA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
